--- a/PE6201_End_of_Course_Project_Dataset.xlsx
+++ b/PE6201_End_of_Course_Project_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e4be5a171166866/NTU入学/PE6201——EMERGING AI TECHNOLOGIES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{95E6A2E6-9DCC-9E4B-90E9-0D170E48DF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F92C54-11A3-5A47-82DC-CE3675657AA5}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{95E6A2E6-9DCC-9E4B-90E9-0D170E48DF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7609AA78-2A6A-F44B-BA37-A3C7F1BD1DDC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{DA4B1C98-A0E4-7447-BDBF-2191DF764DDA}"/>
+    <workbookView xWindow="1180" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{DA4B1C98-A0E4-7447-BDBF-2191DF764DDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Part 1" sheetId="1" r:id="rId1"/>
@@ -36,22 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>Requirement</t>
   </si>
   <si>
-    <t>Label</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Source</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Constraint</t>
-  </si>
-  <si>
     <t>Your report should be within 10 pages and in pdf format.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Deliverable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Provide a comprehensive report on the entire process of your project.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,10 +263,6 @@
   </si>
   <si>
     <t>Upload your sound file to TronClass.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Process</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -432,33 +417,15 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -550,50 +517,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -652,33 +582,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1015,684 +918,500 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D3CA53-A478-5C44-AB5A-097405522CCB}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="144.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="59.5" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="59.5" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17">
+      <c r="A9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17">
+      <c r="A10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17">
+      <c r="A22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="17">
+      <c r="A25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17">
+      <c r="A26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17">
+      <c r="A27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="17">
+      <c r="A38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="17">
+      <c r="A41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17">
+      <c r="A42" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17">
-      <c r="A9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17">
-      <c r="A10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="11" t="s">
+    <row r="59" spans="1:2">
+      <c r="A59" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17">
-      <c r="A22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17">
-      <c r="A25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="17">
-      <c r="A26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17">
-      <c r="A27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="17">
-      <c r="A38" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="17">
-      <c r="A41" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="17">
-      <c r="A42" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
